--- a/Data/Rules/Butchers Block Rules Matrix.xlsx
+++ b/Data/Rules/Butchers Block Rules Matrix.xlsx
@@ -661,7 +661,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="AI2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -804,13 +804,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -831,22 +831,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3">
         <v>0</v>
@@ -858,22 +858,22 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -908,100 +908,100 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="b">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="b">
         <v>0</v>
@@ -1030,100 +1030,100 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="b">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AL5" t="b">
         <v>0</v>
@@ -1152,40 +1152,40 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -1197,31 +1197,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1233,19 +1233,19 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="b">
         <v>0</v>
@@ -1274,100 +1274,100 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="b">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="b">
         <v>0</v>
@@ -1396,100 +1396,100 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="b">
         <v>0</v>
@@ -1518,100 +1518,100 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="b">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="b">
         <v>0</v>
@@ -1640,100 +1640,100 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="b">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="b">
         <v>0</v>

--- a/Data/Rules/Butchers Block Rules Matrix.xlsx
+++ b/Data/Rules/Butchers Block Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
   <si>
     <t>SKU</t>
   </si>
@@ -136,6 +136,9 @@
     <t>HQ_Max</t>
   </si>
   <si>
+    <t>Total Max</t>
+  </si>
+  <si>
     <t>27564</t>
   </si>
   <si>
@@ -145,9 +148,6 @@
     <t>14080</t>
   </si>
   <si>
-    <t>10265</t>
-  </si>
-  <si>
     <t>12642</t>
   </si>
   <si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>BB Beef Trachea Crunch Tubes 4pk</t>
-  </si>
-  <si>
-    <t>BB Knuckle Slices</t>
   </si>
   <si>
     <t>BB Liver Bites 1-lb</t>
@@ -522,10 +519,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -646,16 +643,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -768,16 +768,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -890,16 +893,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>44</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1012,16 +1018,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1030,100 +1039,100 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>4</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>3</v>
+      </c>
+      <c r="Y5">
         <v>5</v>
       </c>
-      <c r="S5">
-        <v>10</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>8</v>
-      </c>
-      <c r="V5">
-        <v>12</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>5</v>
-      </c>
-      <c r="Y5">
-        <v>10</v>
-      </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AH5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AK5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AL5" t="b">
         <v>0</v>
@@ -1134,16 +1143,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>33</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1152,100 +1164,100 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AH6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AL6" t="b">
         <v>0</v>
@@ -1256,16 +1268,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>124</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1274,100 +1289,100 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>13</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>6</v>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
+      <c r="S7">
+        <v>10</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7">
         <v>6</v>
       </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7">
+      <c r="V7">
         <v>8</v>
       </c>
-      <c r="M7">
-        <v>10</v>
-      </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>4</v>
-      </c>
-      <c r="P7">
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>4</v>
+      </c>
+      <c r="Y7">
         <v>6</v>
       </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>10</v>
-      </c>
-      <c r="S7">
-        <v>16</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>6</v>
+      </c>
+      <c r="AB7">
+        <v>8</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>4</v>
+      </c>
+      <c r="AE7">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7">
         <v>12</v>
       </c>
-      <c r="V7">
-        <v>16</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>10</v>
-      </c>
-      <c r="Y7">
-        <v>16</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>8</v>
-      </c>
-      <c r="AB7">
-        <v>10</v>
-      </c>
-      <c r="AC7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>6</v>
-      </c>
-      <c r="AE7">
-        <v>10</v>
-      </c>
-      <c r="AF7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>16</v>
-      </c>
       <c r="AH7">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AL7" t="b">
         <v>0</v>
@@ -1378,16 +1393,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>84</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1414,82 +1432,82 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AH8">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="b">
         <v>0</v>
@@ -1500,16 +1518,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>43</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1518,100 +1539,100 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="S9">
+        <v>20</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>10</v>
+      </c>
+      <c r="V9">
+        <v>12</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>6</v>
+      </c>
+      <c r="AB9">
+        <v>8</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>10</v>
+      </c>
+      <c r="AE9">
+        <v>14</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>9</v>
+      </c>
+      <c r="AH9">
+        <v>11</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
         <v>5</v>
       </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-      <c r="V9">
-        <v>5</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>3</v>
-      </c>
-      <c r="Y9">
-        <v>5</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>2</v>
-      </c>
-      <c r="AB9">
-        <v>4</v>
-      </c>
-      <c r="AC9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>2</v>
-      </c>
-      <c r="AE9">
-        <v>4</v>
-      </c>
-      <c r="AF9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
-      </c>
-      <c r="AH9">
-        <v>4</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>1</v>
-      </c>
       <c r="AK9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AL9" t="b">
         <v>0</v>
@@ -1622,127 +1643,8 @@
       <c r="AN9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:40">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>14</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>5</v>
-      </c>
-      <c r="J10">
-        <v>7</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10">
-        <v>12</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>6</v>
-      </c>
-      <c r="P10">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>15</v>
-      </c>
-      <c r="S10">
-        <v>20</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>10</v>
-      </c>
-      <c r="V10">
-        <v>12</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>10</v>
-      </c>
-      <c r="Y10">
-        <v>15</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>6</v>
-      </c>
-      <c r="AB10">
-        <v>8</v>
-      </c>
-      <c r="AC10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>10</v>
-      </c>
-      <c r="AE10">
-        <v>14</v>
-      </c>
-      <c r="AF10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>9</v>
-      </c>
-      <c r="AH10">
-        <v>11</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>5</v>
-      </c>
-      <c r="AK10">
-        <v>7</v>
-      </c>
-      <c r="AL10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
+      <c r="AO9">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
